--- a/artfynd/A 31378-2025 artfynd.xlsx
+++ b/artfynd/A 31378-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>102613067</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554956.4713212937</v>
+        <v>554956</v>
       </c>
       <c r="R2" t="n">
-        <v>6952692.184956764</v>
+        <v>6952692</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,19 +746,9 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,50 +776,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102627413</v>
+        <v>102627412</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lokmyrbäcken, Ånge, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554948.4130308051</v>
+        <v>554947</v>
       </c>
       <c r="R3" t="n">
-        <v>6952706.741980722</v>
+        <v>6952707</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +849,9 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,55 +893,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102627412</v>
+        <v>102627413</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lokmyrbäcken, Ånge, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554947.0341582617</v>
+        <v>554948</v>
       </c>
       <c r="R4" t="n">
-        <v>6952706.719013087</v>
+        <v>6952707</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,19 +961,9 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,12 +1008,7 @@
         <v>102627409</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555023.0552707643</v>
+        <v>555023</v>
       </c>
       <c r="R5" t="n">
-        <v>6952641.874927438</v>
+        <v>6952642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,19 +1073,9 @@
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,125 +1099,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>120215813</v>
-      </c>
-      <c r="B6" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Lisaviken, N om, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>554978</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6952707</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>130-årig grannaturskog på lågörtsmark</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>1 substratenheter # granhögstubbe och dess låga</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31378-2025 artfynd.xlsx
+++ b/artfynd/A 31378-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102613067</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627412</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627413</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,8 +1119,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102627409</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>